--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.1-8B-Instruct/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.1-8B-Instruct/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>9</v>
+        <v>134</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="G2">
-        <v>409</v>
+        <v>175</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>9</v>
+        <v>197</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>404</v>
+        <v>171</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.1-8B-Instruct/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.1-8B-Instruct/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="D2">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E2">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="G2">
-        <v>175</v>
+        <v>226</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>197</v>
+        <v>167</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>171</v>
+        <v>207</v>
       </c>
       <c r="H3">
         <v>426</v>
